--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/93.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/93.xlsx
@@ -426,13 +426,13 @@
         <v>-11.46663547063787</v>
       </c>
       <c r="E2">
-        <v>-13.85566984307442</v>
+        <v>-14.99846195822809</v>
       </c>
       <c r="F2">
-        <v>-3.578077643023985</v>
+        <v>-4.482977081800734</v>
       </c>
       <c r="G2">
-        <v>-10.20735324317456</v>
+        <v>-9.528651681077491</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.78360173605568</v>
       </c>
       <c r="E3">
-        <v>-15.08352028551416</v>
+        <v>-15.60326683279651</v>
       </c>
       <c r="F3">
-        <v>-3.927509521281706</v>
+        <v>-4.469322273532987</v>
       </c>
       <c r="G3">
-        <v>-9.458448252371706</v>
+        <v>-9.467648258425342</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.0056470582659</v>
       </c>
       <c r="E4">
-        <v>-16.63075494276687</v>
+        <v>-16.19937250879619</v>
       </c>
       <c r="F4">
-        <v>-3.548625868384851</v>
+        <v>-4.501904448587299</v>
       </c>
       <c r="G4">
-        <v>-10.06817459815806</v>
+        <v>-9.413775750864781</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.216449654862526</v>
       </c>
       <c r="E5">
-        <v>-16.15084538133</v>
+        <v>-17.1924668586783</v>
       </c>
       <c r="F5">
-        <v>-3.828328263777118</v>
+        <v>-4.512544827876259</v>
       </c>
       <c r="G5">
-        <v>-9.553550294078351</v>
+        <v>-8.592237390930322</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.416104700664937</v>
       </c>
       <c r="E6">
-        <v>-16.04042307112697</v>
+        <v>-17.47489419711468</v>
       </c>
       <c r="F6">
-        <v>-3.84696735870751</v>
+        <v>-4.57609220481462</v>
       </c>
       <c r="G6">
-        <v>-9.142718213745875</v>
+        <v>-8.595739948110872</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.618495095435196</v>
       </c>
       <c r="E7">
-        <v>-17.43663312022388</v>
+        <v>-18.89941173723354</v>
       </c>
       <c r="F7">
-        <v>-4.042482774953263</v>
+        <v>-4.516168106896105</v>
       </c>
       <c r="G7">
-        <v>-9.038320160164957</v>
+        <v>-7.998464564097721</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.835094675941972</v>
       </c>
       <c r="E8">
-        <v>-18.55610359423804</v>
+        <v>-18.56662323935786</v>
       </c>
       <c r="F8">
-        <v>-4.046226995613917</v>
+        <v>-4.580838750032662</v>
       </c>
       <c r="G8">
-        <v>-8.256670563433177</v>
+        <v>-7.916806647826058</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.078245095906918</v>
       </c>
       <c r="E9">
-        <v>-18.04111194466375</v>
+        <v>-19.57039573095006</v>
       </c>
       <c r="F9">
-        <v>-4.169966861509302</v>
+        <v>-4.68349418042459</v>
       </c>
       <c r="G9">
-        <v>-9.135799173568799</v>
+        <v>-8.019781166825089</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.344976957426617</v>
       </c>
       <c r="E10">
-        <v>-19.08523766813829</v>
+        <v>-19.6610421951616</v>
       </c>
       <c r="F10">
-        <v>-4.051791139458521</v>
+        <v>-4.594727986275401</v>
       </c>
       <c r="G10">
-        <v>-7.947035239145143</v>
+        <v>-7.006227855067361</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.653845818942185</v>
       </c>
       <c r="E11">
-        <v>-20.01981960536729</v>
+        <v>-20.98079801758701</v>
       </c>
       <c r="F11">
-        <v>-3.875560944717343</v>
+        <v>-4.679261222996285</v>
       </c>
       <c r="G11">
-        <v>-8.131906033694664</v>
+        <v>-7.131856437191624</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.011182024063126</v>
       </c>
       <c r="E12">
-        <v>-20.56305534732743</v>
+        <v>-22.19898016802037</v>
       </c>
       <c r="F12">
-        <v>-4.310024736872434</v>
+        <v>-4.827633421981315</v>
       </c>
       <c r="G12">
-        <v>-6.955321596309988</v>
+        <v>-6.916210811309038</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.418389048795464</v>
       </c>
       <c r="E13">
-        <v>-21.71195637391745</v>
+        <v>-22.16823182950829</v>
       </c>
       <c r="F13">
-        <v>-3.85431746267255</v>
+        <v>-4.636981350757399</v>
       </c>
       <c r="G13">
-        <v>-6.497373831862604</v>
+        <v>-6.431391348719391</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.892815603391539</v>
       </c>
       <c r="E14">
-        <v>-21.31218268852031</v>
+        <v>-22.96474965119143</v>
       </c>
       <c r="F14">
-        <v>-4.078700654538463</v>
+        <v>-4.162691310610513</v>
       </c>
       <c r="G14">
-        <v>-6.009488804103592</v>
+        <v>-6.274060982511067</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.436699278139472</v>
       </c>
       <c r="E15">
-        <v>-24.14242460162619</v>
+        <v>-23.14436251575766</v>
       </c>
       <c r="F15">
-        <v>-3.609349340847069</v>
+        <v>-3.968450751797668</v>
       </c>
       <c r="G15">
-        <v>-6.117078223584366</v>
+        <v>-5.875213077030753</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.047983946052577</v>
       </c>
       <c r="E16">
-        <v>-22.98689841756295</v>
+        <v>-24.46611086674645</v>
       </c>
       <c r="F16">
-        <v>-3.194070537740815</v>
+        <v>-3.895035033989757</v>
       </c>
       <c r="G16">
-        <v>-5.492494149417768</v>
+        <v>-5.333670727171232</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.731738552828507</v>
       </c>
       <c r="E17">
-        <v>-24.3357270431176</v>
+        <v>-24.78026469408056</v>
       </c>
       <c r="F17">
-        <v>-3.114350943997599</v>
+        <v>-3.887139864273675</v>
       </c>
       <c r="G17">
-        <v>-5.2759480551485</v>
+        <v>-5.400166344873034</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.478832703794311</v>
       </c>
       <c r="E18">
-        <v>-24.45881096664608</v>
+        <v>-26.22896881387439</v>
       </c>
       <c r="F18">
-        <v>-2.892162925749104</v>
+        <v>-3.33404640473107</v>
       </c>
       <c r="G18">
-        <v>-5.510632628427435</v>
+        <v>-4.998875256784737</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.278030754311567</v>
       </c>
       <c r="E19">
-        <v>-26.29180139073081</v>
+        <v>-26.7766786881541</v>
       </c>
       <c r="F19">
-        <v>-2.495640017377037</v>
+        <v>-3.183488144170052</v>
       </c>
       <c r="G19">
-        <v>-5.516720721674155</v>
+        <v>-5.502548276220534</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.12152090437611</v>
       </c>
       <c r="E20">
-        <v>-27.29817322640341</v>
+        <v>-27.29761169562646</v>
       </c>
       <c r="F20">
-        <v>-2.201615149590367</v>
+        <v>-2.687465056843318</v>
       </c>
       <c r="G20">
-        <v>-4.942053053148687</v>
+        <v>-4.575986169598236</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.99452798579004</v>
       </c>
       <c r="E21">
-        <v>-27.84541666786034</v>
+        <v>-27.79463436033832</v>
       </c>
       <c r="F21">
-        <v>-1.843308971346454</v>
+        <v>-2.473588048747112</v>
       </c>
       <c r="G21">
-        <v>-5.064069830089605</v>
+        <v>-4.527198659985997</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.8869205106384652</v>
       </c>
       <c r="E22">
-        <v>-28.01457781441686</v>
+        <v>-28.22215400598046</v>
       </c>
       <c r="F22">
-        <v>-1.956627975314621</v>
+        <v>-2.213896524704272</v>
       </c>
       <c r="G22">
-        <v>-4.755848108746839</v>
+        <v>-5.286018734678963</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.7940458031001578</v>
       </c>
       <c r="E23">
-        <v>-28.25780668184285</v>
+        <v>-28.13405707263524</v>
       </c>
       <c r="F23">
-        <v>-1.905275823280274</v>
+        <v>-1.691980329100832</v>
       </c>
       <c r="G23">
-        <v>-4.252171778765503</v>
+        <v>-4.256982001434064</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.7109130691567811</v>
       </c>
       <c r="E24">
-        <v>-28.33484055318733</v>
+        <v>-29.77819201670409</v>
       </c>
       <c r="F24">
-        <v>-1.717013592013434</v>
+        <v>-1.702021798757568</v>
       </c>
       <c r="G24">
-        <v>-4.562177884153936</v>
+        <v>-5.182233132022811</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6380411644785091</v>
       </c>
       <c r="E25">
-        <v>-29.88464059096539</v>
+        <v>-29.03895486274396</v>
       </c>
       <c r="F25">
-        <v>-1.431539132558459</v>
+        <v>-1.495048404596292</v>
       </c>
       <c r="G25">
-        <v>-5.291871779192395</v>
+        <v>-4.740149501799616</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.5782098867355604</v>
       </c>
       <c r="E26">
-        <v>-29.81446962197953</v>
+        <v>-29.456380539823</v>
       </c>
       <c r="F26">
-        <v>-1.521638169858753</v>
+        <v>-1.331072248844727</v>
       </c>
       <c r="G26">
-        <v>-4.749683872952716</v>
+        <v>-5.029901689578787</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.5320768105286081</v>
       </c>
       <c r="E27">
-        <v>-29.1109485425179</v>
+        <v>-29.17024890964835</v>
       </c>
       <c r="F27">
-        <v>-1.145184118554309</v>
+        <v>-1.027950250240512</v>
       </c>
       <c r="G27">
-        <v>-5.784315428158983</v>
+        <v>-5.738739147719837</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5013107803273565</v>
       </c>
       <c r="E28">
-        <v>-28.70725319863012</v>
+        <v>-29.44747303144991</v>
       </c>
       <c r="F28">
-        <v>-1.436496911464214</v>
+        <v>-1.508255066099124</v>
       </c>
       <c r="G28">
-        <v>-5.380713579284276</v>
+        <v>-5.559714776592669</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4859286186978508</v>
       </c>
       <c r="E29">
-        <v>-30.44899034298629</v>
+        <v>-29.60751383135499</v>
       </c>
       <c r="F29">
-        <v>-1.239504516139269</v>
+        <v>-1.60294408717833</v>
       </c>
       <c r="G29">
-        <v>-5.077070342422322</v>
+        <v>-5.439412862241094</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4828339653513948</v>
       </c>
       <c r="E30">
-        <v>-29.47718434941424</v>
+        <v>-28.58869774910931</v>
       </c>
       <c r="F30">
-        <v>-0.8731416365357294</v>
+        <v>-1.507280077666029</v>
       </c>
       <c r="G30">
-        <v>-6.255022035114718</v>
+        <v>-5.932442477768133</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.4883251414952219</v>
       </c>
       <c r="E31">
-        <v>-28.55681729209531</v>
+        <v>-28.6825005597042</v>
       </c>
       <c r="F31">
-        <v>-0.9683177376477814</v>
+        <v>-1.387028466903834</v>
       </c>
       <c r="G31">
-        <v>-5.832533523938468</v>
+        <v>-6.376691204774013</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.496308352241233</v>
       </c>
       <c r="E32">
-        <v>-28.1307241157656</v>
+        <v>-29.11700764074017</v>
       </c>
       <c r="F32">
-        <v>-1.184324478336586</v>
+        <v>-1.301028191512592</v>
       </c>
       <c r="G32">
-        <v>-5.459908449674721</v>
+        <v>-6.195018397215428</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.4992125643162912</v>
       </c>
       <c r="E33">
-        <v>-28.10007540368168</v>
+        <v>-27.9531988777169</v>
       </c>
       <c r="F33">
-        <v>-1.391571233740786</v>
+        <v>-1.451141618778307</v>
       </c>
       <c r="G33">
-        <v>-5.178750438115498</v>
+        <v>-6.395912232175021</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.4899904645122803</v>
       </c>
       <c r="E34">
-        <v>-28.87099376179947</v>
+        <v>-27.94151994325112</v>
       </c>
       <c r="F34">
-        <v>-1.503416572099372</v>
+        <v>-1.270421672713955</v>
       </c>
       <c r="G34">
-        <v>-5.331959175127429</v>
+        <v>-6.600705889779876</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4611798891973778</v>
       </c>
       <c r="E35">
-        <v>-27.3721413208447</v>
+        <v>-27.67224782180702</v>
       </c>
       <c r="F35">
-        <v>-1.583151904823242</v>
+        <v>-1.771927723879818</v>
       </c>
       <c r="G35">
-        <v>-5.572443824191167</v>
+        <v>-5.211147436762806</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.4072907184525967</v>
       </c>
       <c r="E36">
-        <v>-28.37892071917799</v>
+        <v>-27.22173258515394</v>
       </c>
       <c r="F36">
-        <v>-1.659403952618339</v>
+        <v>-1.595859889149589</v>
       </c>
       <c r="G36">
-        <v>-4.993167876275034</v>
+        <v>-6.483552304236147</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3249018959753258</v>
       </c>
       <c r="E37">
-        <v>-26.447182390882</v>
+        <v>-26.35976925711194</v>
       </c>
       <c r="F37">
-        <v>-1.737959690160622</v>
+        <v>-1.749293412965724</v>
       </c>
       <c r="G37">
-        <v>-5.452856987676074</v>
+        <v>-6.547425969870845</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2119945228836104</v>
       </c>
       <c r="E38">
-        <v>-24.85466752202659</v>
+        <v>-26.14391048658832</v>
       </c>
       <c r="F38">
-        <v>-1.42188119700922</v>
+        <v>-1.361711902339475</v>
       </c>
       <c r="G38">
-        <v>-6.806462916136659</v>
+        <v>-5.914390072942488</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.07016204334457389</v>
       </c>
       <c r="E39">
-        <v>-25.42756476873696</v>
+        <v>-26.54304565715037</v>
       </c>
       <c r="F39">
-        <v>-1.597780873156681</v>
+        <v>-1.652453121741448</v>
       </c>
       <c r="G39">
-        <v>-5.776416466502282</v>
+        <v>-5.714929704201399</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.09713014384691039</v>
       </c>
       <c r="E40">
-        <v>-24.16319671189937</v>
+        <v>-25.07479664353945</v>
       </c>
       <c r="F40">
-        <v>-1.557474172071263</v>
+        <v>-1.797720599700786</v>
       </c>
       <c r="G40">
-        <v>-5.346919530419396</v>
+        <v>-6.004496501430371</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.284868896318992</v>
       </c>
       <c r="E41">
-        <v>-23.92927838703316</v>
+        <v>-24.39661690462474</v>
       </c>
       <c r="F41">
-        <v>-1.692846801404161</v>
+        <v>-1.802945941277646</v>
       </c>
       <c r="G41">
-        <v>-5.570877936151091</v>
+        <v>-5.690613747215452</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.4846065909799519</v>
       </c>
       <c r="E42">
-        <v>-24.02992372185363</v>
+        <v>-23.86336191937751</v>
       </c>
       <c r="F42">
-        <v>-1.849931768731836</v>
+        <v>-1.728044132349112</v>
       </c>
       <c r="G42">
-        <v>-4.785636397509202</v>
+        <v>-5.457405677247032</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.6872030585390716</v>
       </c>
       <c r="E43">
-        <v>-24.13876559462799</v>
+        <v>-23.70553554326218</v>
       </c>
       <c r="F43">
-        <v>-2.110611535086216</v>
+        <v>-1.959825473489427</v>
       </c>
       <c r="G43">
-        <v>-5.408204349442384</v>
+        <v>-5.38973481587879</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.8821319507938292</v>
       </c>
       <c r="E44">
-        <v>-22.72978977730346</v>
+        <v>-24.2622208530251</v>
       </c>
       <c r="F44">
-        <v>-1.888017616810349</v>
+        <v>-1.900366918051284</v>
       </c>
       <c r="G44">
-        <v>-4.845037516120344</v>
+        <v>-5.351630436721779</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.057210158366172</v>
       </c>
       <c r="E45">
-        <v>-21.19797457404686</v>
+        <v>-22.33655520837339</v>
       </c>
       <c r="F45">
-        <v>-1.60590301554113</v>
+        <v>-2.001206567096276</v>
       </c>
       <c r="G45">
-        <v>-4.663920880212357</v>
+        <v>-5.771450648193376</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.200613865071289</v>
       </c>
       <c r="E46">
-        <v>-21.98665813569674</v>
+        <v>-21.60827243303783</v>
       </c>
       <c r="F46">
-        <v>-2.03384507113398</v>
+        <v>-2.224795354622905</v>
       </c>
       <c r="G46">
-        <v>-5.147300255492421</v>
+        <v>-4.914135222616013</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.300778619686693</v>
       </c>
       <c r="E47">
-        <v>-20.08557304795867</v>
+        <v>-21.1334121201195</v>
       </c>
       <c r="F47">
-        <v>-1.804787402014069</v>
+        <v>-2.317774625382733</v>
       </c>
       <c r="G47">
-        <v>-5.047093352564223</v>
+        <v>-5.466311044747671</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.34766285360947</v>
       </c>
       <c r="E48">
-        <v>-21.13779115448492</v>
+        <v>-21.45847051286409</v>
       </c>
       <c r="F48">
-        <v>-1.586573062196804</v>
+        <v>-2.278364217827144</v>
       </c>
       <c r="G48">
-        <v>-5.629444797286338</v>
+        <v>-5.7756086933907</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.332544429887938</v>
       </c>
       <c r="E49">
-        <v>-19.89120188660144</v>
+        <v>-20.08861618249182</v>
       </c>
       <c r="F49">
-        <v>-1.756147324856488</v>
+        <v>-2.302303207400647</v>
       </c>
       <c r="G49">
-        <v>-4.288730133155675</v>
+        <v>-5.300075311038708</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.250860677599593</v>
       </c>
       <c r="E50">
-        <v>-18.82007740109316</v>
+        <v>-18.74333335208517</v>
       </c>
       <c r="F50">
-        <v>-1.679766880113956</v>
+        <v>-2.332849255378878</v>
       </c>
       <c r="G50">
-        <v>-6.063987004771074</v>
+        <v>-6.041783175839182</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.102595869104513</v>
       </c>
       <c r="E51">
-        <v>-18.42323363837898</v>
+        <v>-18.80670934582252</v>
       </c>
       <c r="F51">
-        <v>-1.843112648271991</v>
+        <v>-2.331204946084321</v>
       </c>
       <c r="G51">
-        <v>-5.104885546043279</v>
+        <v>-5.665132478199681</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.888817963065857</v>
       </c>
       <c r="E52">
-        <v>-17.4505219500054</v>
+        <v>-18.66921128952762</v>
       </c>
       <c r="F52">
-        <v>-1.674588755479057</v>
+        <v>-2.407687280017397</v>
       </c>
       <c r="G52">
-        <v>-5.121031076638305</v>
+        <v>-5.703170646445908</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.6149013313885998</v>
       </c>
       <c r="E53">
-        <v>-17.18081962353058</v>
+        <v>-18.04806768073953</v>
       </c>
       <c r="F53">
-        <v>-1.982950177905978</v>
+        <v>-2.381439630492292</v>
       </c>
       <c r="G53">
-        <v>-6.184338577305739</v>
+        <v>-6.134392376754755</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.2901655798513162</v>
       </c>
       <c r="E54">
-        <v>-17.02694660522395</v>
+        <v>-17.87869369590464</v>
       </c>
       <c r="F54">
-        <v>-1.817175636522936</v>
+        <v>-2.372595151732601</v>
       </c>
       <c r="G54">
-        <v>-6.058925180641529</v>
+        <v>-6.244458084298904</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.07737378667865462</v>
       </c>
       <c r="E55">
-        <v>-17.12318120636095</v>
+        <v>-17.31949961154147</v>
       </c>
       <c r="F55">
-        <v>-2.032621572480045</v>
+        <v>-2.692050070417814</v>
       </c>
       <c r="G55">
-        <v>-5.594737037852619</v>
+        <v>-6.567997699851877</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.4762966038886624</v>
       </c>
       <c r="E56">
-        <v>-15.49410796684161</v>
+        <v>-16.47159719529329</v>
       </c>
       <c r="F56">
-        <v>-1.836902377853203</v>
+        <v>-2.43822173085199</v>
       </c>
       <c r="G56">
-        <v>-6.620320872100057</v>
+        <v>-6.190525986918637</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.8932566583404871</v>
       </c>
       <c r="E57">
-        <v>-16.41306214027015</v>
+        <v>-16.82043460505216</v>
       </c>
       <c r="F57">
-        <v>-1.963036225542678</v>
+        <v>-2.7728556538261</v>
       </c>
       <c r="G57">
-        <v>-6.559009568712756</v>
+        <v>-6.48812747817142</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.318046767115645</v>
       </c>
       <c r="E58">
-        <v>-14.85497273082104</v>
+        <v>-16.50582340184327</v>
       </c>
       <c r="F58">
-        <v>-1.92386273106429</v>
+        <v>-2.50716012284777</v>
       </c>
       <c r="G58">
-        <v>-6.494629389610549</v>
+        <v>-6.335918525912349</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.737743664016174</v>
       </c>
       <c r="E59">
-        <v>-14.27478011248431</v>
+        <v>-15.24508718115982</v>
       </c>
       <c r="F59">
-        <v>-2.085690930140395</v>
+        <v>-2.882923315738279</v>
       </c>
       <c r="G59">
-        <v>-7.218109390671795</v>
+        <v>-6.512029616964958</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.139524577057906</v>
       </c>
       <c r="E60">
-        <v>-15.38979003960092</v>
+        <v>-14.87381118269295</v>
       </c>
       <c r="F60">
-        <v>-2.295911524520645</v>
+        <v>-2.647277640663904</v>
       </c>
       <c r="G60">
-        <v>-7.448910694033165</v>
+        <v>-6.655157742809808</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.514963163460827</v>
       </c>
       <c r="E61">
-        <v>-14.17264490971531</v>
+        <v>-14.19936290636057</v>
       </c>
       <c r="F61">
-        <v>-2.030085939860076</v>
+        <v>-2.725955148214398</v>
       </c>
       <c r="G61">
-        <v>-7.781746321460411</v>
+        <v>-6.89626146388939</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.854315378209913</v>
       </c>
       <c r="E62">
-        <v>-13.77192930172458</v>
+        <v>-14.6995600313518</v>
       </c>
       <c r="F62">
-        <v>-2.075834186414484</v>
+        <v>-2.836113930540884</v>
       </c>
       <c r="G62">
-        <v>-7.428550838966647</v>
+        <v>-7.441203744017741</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.151197575520888</v>
       </c>
       <c r="E63">
-        <v>-14.31754249253874</v>
+        <v>-14.74718146401647</v>
       </c>
       <c r="F63">
-        <v>-2.566698201556581</v>
+        <v>-2.853971875010436</v>
       </c>
       <c r="G63">
-        <v>-7.45361166869893</v>
+        <v>-7.965868932718057</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.403224999201433</v>
       </c>
       <c r="E64">
-        <v>-14.67189105516494</v>
+        <v>-13.32119216984512</v>
       </c>
       <c r="F64">
-        <v>-2.177710123080379</v>
+        <v>-3.05530491552605</v>
       </c>
       <c r="G64">
-        <v>-7.303422149218814</v>
+        <v>-7.551706443573075</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.605949436023468</v>
       </c>
       <c r="E65">
-        <v>-13.24501418008809</v>
+        <v>-13.35488401646218</v>
       </c>
       <c r="F65">
-        <v>-2.236862182579486</v>
+        <v>-2.738099014339439</v>
       </c>
       <c r="G65">
-        <v>-8.118826068269003</v>
+        <v>-7.089848924843812</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.760058669274102</v>
       </c>
       <c r="E66">
-        <v>-12.98517939847598</v>
+        <v>-14.5265134540967</v>
       </c>
       <c r="F66">
-        <v>-2.439642380947791</v>
+        <v>-3.136166827917727</v>
       </c>
       <c r="G66">
-        <v>-7.032546692104567</v>
+        <v>-7.815931014698926</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.867752798101541</v>
       </c>
       <c r="E67">
-        <v>-13.42147522674498</v>
+        <v>-13.06584963444862</v>
       </c>
       <c r="F67">
-        <v>-2.403943059356743</v>
+        <v>-2.896077790094735</v>
       </c>
       <c r="G67">
-        <v>-7.943046031770321</v>
+        <v>-7.363362886752858</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.928703889439292</v>
       </c>
       <c r="E68">
-        <v>-13.54282474472852</v>
+        <v>-13.16702480072799</v>
       </c>
       <c r="F68">
-        <v>-2.802445765821501</v>
+        <v>-3.054903985703096</v>
       </c>
       <c r="G68">
-        <v>-8.76322375748814</v>
+        <v>-7.7347398853483</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.949248918647976</v>
       </c>
       <c r="E69">
-        <v>-13.08915316169209</v>
+        <v>-13.97542986668127</v>
       </c>
       <c r="F69">
-        <v>-2.640518991024462</v>
+        <v>-3.150717929715303</v>
       </c>
       <c r="G69">
-        <v>-7.172053081129454</v>
+        <v>-7.97235429142949</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.933416073008276</v>
       </c>
       <c r="E70">
-        <v>-12.69945533096202</v>
+        <v>-14.16270038079447</v>
       </c>
       <c r="F70">
-        <v>-2.511207525977848</v>
+        <v>-3.1545043971135</v>
       </c>
       <c r="G70">
-        <v>-8.702011770467015</v>
+        <v>-8.045179672202377</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.883131952155629</v>
       </c>
       <c r="E71">
-        <v>-12.20212473001763</v>
+        <v>-13.93983606098098</v>
       </c>
       <c r="F71">
-        <v>-2.8321535059881</v>
+        <v>-3.222386620670711</v>
       </c>
       <c r="G71">
-        <v>-8.180657127305972</v>
+        <v>-7.854008909491623</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.80539204476451</v>
       </c>
       <c r="E72">
-        <v>-13.01582358208588</v>
+        <v>-13.59177302027743</v>
       </c>
       <c r="F72">
-        <v>-2.704977572105903</v>
+        <v>-3.350332107870108</v>
       </c>
       <c r="G72">
-        <v>-8.177045322122627</v>
+        <v>-7.3074841885955</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.703402795962191</v>
       </c>
       <c r="E73">
-        <v>-13.5073305654564</v>
+        <v>-13.42742564159106</v>
       </c>
       <c r="F73">
-        <v>-3.116950360907584</v>
+        <v>-3.298794401537534</v>
       </c>
       <c r="G73">
-        <v>-7.995203676741539</v>
+        <v>-7.56289939804135</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.580182926762157</v>
       </c>
       <c r="E74">
-        <v>-14.06287469976938</v>
+        <v>-13.65873103695484</v>
       </c>
       <c r="F74">
-        <v>-2.605932995222777</v>
+        <v>-3.383956369117143</v>
       </c>
       <c r="G74">
-        <v>-7.473329277930829</v>
+        <v>-7.256736836024012</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.441303570378706</v>
       </c>
       <c r="E75">
-        <v>-13.9807598805883</v>
+        <v>-14.09353699727532</v>
       </c>
       <c r="F75">
-        <v>-2.811170959675188</v>
+        <v>-3.52012174605452</v>
       </c>
       <c r="G75">
-        <v>-6.642948450860977</v>
+        <v>-7.415030570984263</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.287093436245502</v>
       </c>
       <c r="E76">
-        <v>-14.65820600671376</v>
+        <v>-13.62584073023713</v>
       </c>
       <c r="F76">
-        <v>-2.755547745312007</v>
+        <v>-3.398165355177363</v>
       </c>
       <c r="G76">
-        <v>-7.796882135665959</v>
+        <v>-6.695364318384257</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.120023761120466</v>
       </c>
       <c r="E77">
-        <v>-14.40304008180356</v>
+        <v>-14.24312607917069</v>
       </c>
       <c r="F77">
-        <v>-3.17813192054355</v>
+        <v>-3.791918202954469</v>
       </c>
       <c r="G77">
-        <v>-7.118849303767828</v>
+        <v>-6.842047970138285</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.943985420938134</v>
       </c>
       <c r="E78">
-        <v>-14.6160142143843</v>
+        <v>-15.18864880960223</v>
       </c>
       <c r="F78">
-        <v>-2.867879335336037</v>
+        <v>-3.521152235103603</v>
       </c>
       <c r="G78">
-        <v>-6.636456471058466</v>
+        <v>-6.13718316664436</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.757776279187368</v>
       </c>
       <c r="E79">
-        <v>-16.07646519575401</v>
+        <v>-15.50929646866334</v>
       </c>
       <c r="F79">
-        <v>-2.986467584353411</v>
+        <v>-3.797876649682805</v>
       </c>
       <c r="G79">
-        <v>-6.392621549908986</v>
+        <v>-5.914999213321714</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.563622725563211</v>
       </c>
       <c r="E80">
-        <v>-16.26599541839704</v>
+        <v>-16.22928760809087</v>
       </c>
       <c r="F80">
-        <v>-3.270972025579707</v>
+        <v>-3.967069863337202</v>
       </c>
       <c r="G80">
-        <v>-6.360644990545165</v>
+        <v>-6.587659029809608</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.364396421518117</v>
       </c>
       <c r="E81">
-        <v>-16.15783734519784</v>
+        <v>-17.05728738107534</v>
       </c>
       <c r="F81">
-        <v>-3.153036530075739</v>
+        <v>-3.663913901669472</v>
       </c>
       <c r="G81">
-        <v>-6.229567250463262</v>
+        <v>-6.066966495756418</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.160389386824044</v>
       </c>
       <c r="E82">
-        <v>-17.64910459218976</v>
+        <v>-17.66334664294389</v>
       </c>
       <c r="F82">
-        <v>-3.679056457792647</v>
+        <v>-3.714084801787427</v>
       </c>
       <c r="G82">
-        <v>-6.087849417018141</v>
+        <v>-6.084734193665686</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.959299884292433</v>
       </c>
       <c r="E83">
-        <v>-18.38221924929152</v>
+        <v>-18.53121962956589</v>
       </c>
       <c r="F83">
-        <v>-3.060377837500794</v>
+        <v>-4.055816176668724</v>
       </c>
       <c r="G83">
-        <v>-6.682234694775508</v>
+        <v>-5.859060925344648</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.769641754486353</v>
       </c>
       <c r="E84">
-        <v>-20.74846918709748</v>
+        <v>-19.10310702657256</v>
       </c>
       <c r="F84">
-        <v>-3.719529660726028</v>
+        <v>-4.193317710226816</v>
       </c>
       <c r="G84">
-        <v>-6.057432124603317</v>
+        <v>-5.278384616665404</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.597184299002926</v>
       </c>
       <c r="E85">
-        <v>-19.88551412324781</v>
+        <v>-20.5330496785526</v>
       </c>
       <c r="F85">
-        <v>-3.608238500159915</v>
+        <v>-4.174223841592288</v>
       </c>
       <c r="G85">
-        <v>-6.320067633870318</v>
+        <v>-5.379505230162442</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.454123312455341</v>
       </c>
       <c r="E86">
-        <v>-20.77055455483289</v>
+        <v>-21.77950309221585</v>
       </c>
       <c r="F86">
-        <v>-3.12258905781844</v>
+        <v>-4.385860115863923</v>
       </c>
       <c r="G86">
-        <v>-5.366756319290709</v>
+        <v>-5.696804467373889</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.351302185718147</v>
       </c>
       <c r="E87">
-        <v>-21.68557801282277</v>
+        <v>-21.91111413230078</v>
       </c>
       <c r="F87">
-        <v>-3.821511628419481</v>
+        <v>-4.066554303311214</v>
       </c>
       <c r="G87">
-        <v>-5.674262962796991</v>
+        <v>-4.906239571504851</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.294293270452962</v>
       </c>
       <c r="E88">
-        <v>-22.91999474257363</v>
+        <v>-23.99899424438124</v>
       </c>
       <c r="F88">
-        <v>-3.741566718742703</v>
+        <v>-4.207221857082806</v>
       </c>
       <c r="G88">
-        <v>-5.245020938720629</v>
+        <v>-4.930168194662703</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.29503826458447</v>
       </c>
       <c r="E89">
-        <v>-24.85395655160739</v>
+        <v>-24.29979813034075</v>
       </c>
       <c r="F89">
-        <v>-3.429605211583215</v>
+        <v>-4.391604015434934</v>
       </c>
       <c r="G89">
-        <v>-5.314823791416162</v>
+        <v>-4.74667127651198</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.361465004006263</v>
       </c>
       <c r="E90">
-        <v>-25.24458724798304</v>
+        <v>-26.51222033458016</v>
       </c>
       <c r="F90">
-        <v>-3.864563539077777</v>
+        <v>-4.368301212026782</v>
       </c>
       <c r="G90">
-        <v>-4.353087138439107</v>
+        <v>-4.605526167445153</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.493502968050385</v>
       </c>
       <c r="E91">
-        <v>-26.36243199982845</v>
+        <v>-28.19599301163815</v>
       </c>
       <c r="F91">
-        <v>-3.430702798391925</v>
+        <v>-4.674014343866953</v>
       </c>
       <c r="G91">
-        <v>-4.890653523105962</v>
+        <v>-5.621085669799679</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.695930245334184</v>
       </c>
       <c r="E92">
-        <v>-29.27474797584935</v>
+        <v>-29.34060104486889</v>
       </c>
       <c r="F92">
-        <v>-3.204182418626789</v>
+        <v>-4.595904267987376</v>
       </c>
       <c r="G92">
-        <v>-4.518180733937021</v>
+        <v>-5.149690469371776</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.967011264369454</v>
       </c>
       <c r="E93">
-        <v>-30.43386523980067</v>
+        <v>-31.66885708575051</v>
       </c>
       <c r="F93">
-        <v>-3.815431411682932</v>
+        <v>-4.679393761780733</v>
       </c>
       <c r="G93">
-        <v>-5.466632167664981</v>
+        <v>-5.125036836740823</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.295834708564142</v>
       </c>
       <c r="E94">
-        <v>-32.65312317555466</v>
+        <v>-33.57925950875936</v>
       </c>
       <c r="F94">
-        <v>-4.16277911755521</v>
+        <v>-4.768994950271944</v>
       </c>
       <c r="G94">
-        <v>-5.581597482607251</v>
+        <v>-5.287382679441142</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.676242225189915</v>
       </c>
       <c r="E95">
-        <v>-34.50787291724625</v>
+        <v>-36.23093237055777</v>
       </c>
       <c r="F95">
-        <v>-4.019722552193944</v>
+        <v>-4.829444233123835</v>
       </c>
       <c r="G95">
-        <v>-5.684062177593234</v>
+        <v>-5.404913667176348</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.096210165405587</v>
       </c>
       <c r="E96">
-        <v>-36.6570844170496</v>
+        <v>-36.59200118861136</v>
       </c>
       <c r="F96">
-        <v>-4.067454738678057</v>
+        <v>-4.850949479267913</v>
       </c>
       <c r="G96">
-        <v>-5.791320542520081</v>
+        <v>-6.108781996462953</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.531263054528356</v>
       </c>
       <c r="E97">
-        <v>-38.66010998317433</v>
+        <v>-39.21017466393803</v>
       </c>
       <c r="F97">
-        <v>-4.263546698636159</v>
+        <v>-5.110784310871437</v>
       </c>
       <c r="G97">
-        <v>-5.836741227318882</v>
+        <v>-6.220380486591784</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.972710641010363</v>
       </c>
       <c r="E98">
-        <v>-40.73803650938594</v>
+        <v>-41.46798802739333</v>
       </c>
       <c r="F98">
-        <v>-4.730425335630197</v>
+        <v>-5.167117436098818</v>
       </c>
       <c r="G98">
-        <v>-6.849999900523614</v>
+        <v>-6.443918453039992</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.392436034110205</v>
       </c>
       <c r="E99">
-        <v>-42.29771994168574</v>
+        <v>-43.2370024349347</v>
       </c>
       <c r="F99">
-        <v>-4.84942445487936</v>
+        <v>-5.31693099436472</v>
       </c>
       <c r="G99">
-        <v>-8.040697193542204</v>
+        <v>-7.163819754373288</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.785971496335696</v>
       </c>
       <c r="E100">
-        <v>-44.5658989821446</v>
+        <v>-44.71730398211704</v>
       </c>
       <c r="F100">
-        <v>-4.470023072355755</v>
+        <v>-5.652298850857711</v>
       </c>
       <c r="G100">
-        <v>-7.619522968945045</v>
+        <v>-7.545677940146062</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.120468029275263</v>
       </c>
       <c r="E101">
-        <v>-47.19156481771697</v>
+        <v>-47.2755363112412</v>
       </c>
       <c r="F101">
-        <v>-5.002831470938606</v>
+        <v>-5.559495193987276</v>
       </c>
       <c r="G101">
-        <v>-7.222916302794817</v>
+        <v>-7.593310069365096</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.426161993252657</v>
       </c>
       <c r="E102">
-        <v>-49.57120658528212</v>
+        <v>-49.70242930872088</v>
       </c>
       <c r="F102">
-        <v>-4.946871939409887</v>
+        <v>-5.687197141170251</v>
       </c>
       <c r="G102">
-        <v>-7.489689993985907</v>
+        <v>-8.07691456174183</v>
       </c>
     </row>
   </sheetData>
